--- a/config/组合测控/温湿度控制器_爱可信.xlsx
+++ b/config/组合测控/温湿度控制器_爱可信.xlsx
@@ -1322,7 +1322,7 @@
     <col min="7" max="7" width="14.3888888888889" customWidth="1"/>
     <col min="9" max="9" width="10.8412698412698" customWidth="1"/>
     <col min="13" max="13" width="18.8412698412698" customWidth="1"/>
-    <col min="14" max="14" width="27.2301587301587" customWidth="1"/>
+    <col min="14" max="14" width="30.7539682539683" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
